--- a/시장조사_2026-05-28.xlsx
+++ b/시장조사_2026-05-28.xlsx
@@ -444,7 +444,7 @@
         <v>유정란</v>
       </c>
       <c r="C2">
-        <v>3500</v>
+        <v>7600</v>
       </c>
       <c r="D2">
         <v>7600</v>
@@ -456,10 +456,10 @@
         <v/>
       </c>
       <c r="G2">
-        <v>17500</v>
+        <v>9260</v>
       </c>
       <c r="H2" t="str">
-        <v>유정란전병 조합원 3,500 원 비조합원 3,850 원</v>
+        <v>강화유정란(15구) 조합원 7,600 원 비조합원 8,360 원</v>
       </c>
     </row>
     <row r="3">
@@ -467,10 +467,10 @@
         <v>축산</v>
       </c>
       <c r="B3" t="str">
-        <v>돼지삼겹살</v>
+        <v>삼겹살</v>
       </c>
       <c r="C3">
-        <v>17500</v>
+        <v>22200</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -481,11 +481,11 @@
       <c r="F3" t="str">
         <v/>
       </c>
-      <c r="G3" t="str">
-        <v/>
+      <c r="G3">
+        <v>16400</v>
       </c>
       <c r="H3" t="str">
-        <v>돼지삼겹살(400g) 조합원 17,500 원 비조합원 19,250 원</v>
+        <v>돼지삼겹살(600g/냉동) 조합원 22,200 원 비조합원 24,420 원</v>
       </c>
     </row>
     <row r="4">
@@ -493,10 +493,10 @@
         <v>축산</v>
       </c>
       <c r="B4" t="str">
-        <v>돼지목살</v>
-      </c>
-      <c r="C4">
-        <v>16500</v>
+        <v>목살</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -507,11 +507,11 @@
       <c r="F4" t="str">
         <v/>
       </c>
-      <c r="G4" t="str">
-        <v/>
+      <c r="G4">
+        <v>16700</v>
       </c>
       <c r="H4" t="str">
-        <v>돼지목살(400g) 조합원 16,500원 14,800 원 비조합원 18,150 원</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -521,11 +521,11 @@
       <c r="B5" t="str">
         <v>돼지불고기</v>
       </c>
-      <c r="C5">
-        <v>10000</v>
+      <c r="C5" t="str">
+        <v/>
       </c>
       <c r="D5">
-        <v>7500</v>
+        <v>19500</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -534,10 +534,10 @@
         <v/>
       </c>
       <c r="G5">
-        <v>6980</v>
+        <v>18350</v>
       </c>
       <c r="H5" t="str">
-        <v>돼지불고기 주간생활재 장바구니 돼지뒷다리살 불고기(600g/냉동) 조합원 10,000 원 비조합원 11,000 원 장바구니 돼지뒷다리살(500g</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -547,11 +547,11 @@
       <c r="B6" t="str">
         <v>한우국거리</v>
       </c>
-      <c r="C6">
-        <v>19200</v>
+      <c r="C6" t="str">
+        <v/>
       </c>
       <c r="D6">
-        <v>40600</v>
+        <v>24400</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -559,11 +559,11 @@
       <c r="F6" t="str">
         <v/>
       </c>
-      <c r="G6" t="str">
-        <v/>
+      <c r="G6">
+        <v>15900</v>
       </c>
       <c r="H6" t="str">
-        <v>온)한우국거리300g 조합원 19,200 원 비조합원 21,120 원</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -573,11 +573,11 @@
       <c r="B7" t="str">
         <v>한우등심</v>
       </c>
-      <c r="C7">
-        <v>30100</v>
-      </c>
-      <c r="D7">
-        <v>24600</v>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -585,11 +585,11 @@
       <c r="F7" t="str">
         <v/>
       </c>
-      <c r="G7" t="str">
-        <v/>
+      <c r="G7">
+        <v>37900</v>
       </c>
       <c r="H7" t="str">
-        <v>온)한우등심로스300g 조합원 30,100 원 비조합원 33,110 원</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -599,11 +599,11 @@
       <c r="B8" t="str">
         <v>한우불고기</v>
       </c>
-      <c r="C8">
-        <v>19800</v>
+      <c r="C8" t="str">
+        <v/>
       </c>
       <c r="D8">
-        <v>4050</v>
+        <v>40800</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -612,10 +612,10 @@
         <v/>
       </c>
       <c r="G8">
-        <v>5900</v>
+        <v>12490</v>
       </c>
       <c r="H8" t="str">
-        <v>온)한우불고기300g 조합원 19,800 원 비조합원 21,780 원</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -626,10 +626,10 @@
         <v>고등어</v>
       </c>
       <c r="C9">
-        <v>3700</v>
+        <v>20400</v>
       </c>
       <c r="D9">
-        <v>4400</v>
+        <v>12500</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -638,10 +638,10 @@
         <v/>
       </c>
       <c r="G9">
-        <v>3980</v>
+        <v>12900</v>
       </c>
       <c r="H9" t="str">
-        <v>고등어구이(90g) 조합원 3,700 원 비조합원 4,070 원</v>
+        <v>순살고등어(800g/노르웨이) 조합원 20,400 원 비조합원 22,440 원</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
         <v>34500</v>
       </c>
       <c r="D10">
-        <v>22200</v>
+        <v>18000</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -664,7 +664,7 @@
         <v/>
       </c>
       <c r="G10">
-        <v>3000</v>
+        <v>29800</v>
       </c>
       <c r="H10" t="str">
         <v>제주은갈치(400g) 조합원 34,500 원 비조합원 37,950 원</v>
@@ -678,10 +678,10 @@
         <v>삼치</v>
       </c>
       <c r="C11">
-        <v>3900</v>
+        <v>18400</v>
       </c>
       <c r="D11">
-        <v>4000</v>
+        <v>13500</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -693,7 +693,7 @@
         <v>9900</v>
       </c>
       <c r="H11" t="str">
-        <v>삼치구이(90g) 조합원 3,900 원 비조합원 4,290 원</v>
+        <v>순살삼치(1kg) 조합원 18,400 원 비조합원 20,240 원</v>
       </c>
     </row>
     <row r="12">
@@ -704,10 +704,10 @@
         <v>오징어</v>
       </c>
       <c r="C12">
-        <v>15600</v>
+        <v>13000</v>
       </c>
       <c r="D12">
-        <v>17000</v>
+        <v>13600</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -716,10 +716,10 @@
         <v/>
       </c>
       <c r="G12">
-        <v>1360</v>
+        <v>9900</v>
       </c>
       <c r="H12" t="str">
-        <v>손질오징어채 조합원 15,600 원 비조합원 17,160 원</v>
+        <v>손질갑오징어(300g) 조합원 13,000 원 비조합원 14,300 원</v>
       </c>
     </row>
     <row r="13">
@@ -730,10 +730,10 @@
         <v>황태</v>
       </c>
       <c r="C13">
-        <v>6100</v>
+        <v>32800</v>
       </c>
       <c r="D13">
-        <v>15800</v>
+        <v>6800</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -745,7 +745,7 @@
         <v>6980</v>
       </c>
       <c r="H13" t="str">
-        <v>황태콩나물국 조합원 6,100 원 비조합원 6,710 원</v>
+        <v>대관령 황태채(400g) 조합원 32,800 원 비조합원 36,080 원</v>
       </c>
     </row>
     <row r="14">
@@ -756,10 +756,10 @@
         <v>미역</v>
       </c>
       <c r="C14">
-        <v>5800</v>
+        <v>2800</v>
       </c>
       <c r="D14">
-        <v>5300</v>
+        <v>3400</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -768,10 +768,10 @@
         <v/>
       </c>
       <c r="G14">
-        <v>5500</v>
+        <v>4000</v>
       </c>
       <c r="H14" t="str">
-        <v>들깨미역국 조합원 5,800 원 비조합원 6,380 원</v>
+        <v>자른미역(45g) 조합원 2,800 원 비조합원 3,080 원</v>
       </c>
     </row>
     <row r="15">
@@ -782,22 +782,22 @@
         <v>김</v>
       </c>
       <c r="C15">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="D15">
-        <v>8500</v>
-      </c>
-      <c r="E15">
-        <v>8200</v>
+        <v>2850</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
       </c>
       <c r="F15" t="str">
         <v/>
       </c>
       <c r="G15">
-        <v>6980</v>
+        <v>15900</v>
       </c>
       <c r="H15" t="str">
-        <v>김부각 조합원 3,200 원 비조합원 3,520 원</v>
+        <v>햇살바다조미김(도시락/9개입) 조합원 3,500 원 비조합원 3,850 원</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C12"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -827,9 +827,130 @@
         <v>기획가</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>32215</v>
+      </c>
+      <c r="B2" t="str">
+        <v>돼지앞다리살(500g/불고기용)</v>
+      </c>
+      <c r="C2">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>38013</v>
+      </c>
+      <c r="B3" t="str">
+        <v>돼지다짐육(1kg/뒷다리/냉동)</v>
+      </c>
+      <c r="C3">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>42155</v>
+      </c>
+      <c r="B4" t="str">
+        <v>한우불고기(500g)</v>
+      </c>
+      <c r="C4">
+        <v>30200</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>42161</v>
+      </c>
+      <c r="B5" t="str">
+        <v>한우국거리(500g)</v>
+      </c>
+      <c r="C5">
+        <v>28100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>42164</v>
+      </c>
+      <c r="B6" t="str">
+        <v>한우장조림(500g/냉장)</v>
+      </c>
+      <c r="C6">
+        <v>29200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>55284</v>
+      </c>
+      <c r="B7" t="str">
+        <v>한우국거리(500g/냉동/대)</v>
+      </c>
+      <c r="C7">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>58374</v>
+      </c>
+      <c r="B8" t="str">
+        <v>돼지목살(400g)</v>
+      </c>
+      <c r="C8">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>52231</v>
+      </c>
+      <c r="B9" t="str">
+        <v>닭발(1kg/냉동)</v>
+      </c>
+      <c r="C9">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>52232</v>
+      </c>
+      <c r="B10" t="str">
+        <v>무뼈닭발(350g/냉동)</v>
+      </c>
+      <c r="C10">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>52233</v>
+      </c>
+      <c r="B11" t="str">
+        <v>닭근위(350g/냉동)</v>
+      </c>
+      <c r="C11">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>52234</v>
+      </c>
+      <c r="B12" t="str">
+        <v>닭목살(350g/냉동)</v>
+      </c>
+      <c r="C12">
+        <v>4900</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>